--- a/game/assets/Background Image Credits.xlsx
+++ b/game/assets/Background Image Credits.xlsx
@@ -964,7 +964,7 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="43.25"/>
     <col customWidth="1" min="2" max="2" width="34.63"/>
-    <col customWidth="1" min="3" max="3" width="16.63"/>
+    <col customWidth="1" min="3" max="3" width="38.5"/>
   </cols>
   <sheetData>
     <row r="1">
